--- a/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_集計データ整理_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_集計データ整理_20260805.xlsx
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>認定率は県内2位だが給付月額は県内中位。利用支援が課題か供給確保が課題かを判別する必要があるとしていた</t>
+          <t>認定率は県内でも高い方にあるが給付月額は県内中位。利用支援が課題か供給確保が課題かを判別する必要があるとしていた</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
